--- a/Archivos_Compartidos/Cursos RH/Manual de conducta respuestas.xlsx
+++ b/Archivos_Compartidos/Cursos RH/Manual de conducta respuestas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\N877991\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://santandernet-my.sharepoint.com/personal/n854611_corp_santanderam_com/Documents/Documentos/GitHub/SAM_Santander/SAM_Santander/Archivos_Compartidos/Cursos RH/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F75462B4-5EB5-40ED-A25C-40A7B9D4CF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{F75462B4-5EB5-40ED-A25C-40A7B9D4CF70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3E009CE-5577-4686-9048-E54028BBE55F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" xr2:uid="{85AF77C6-D4E5-423E-95BD-04F2A6181AE5}"/>
+    <workbookView xWindow="12495" yWindow="0" windowWidth="12810" windowHeight="15135" xr2:uid="{85AF77C6-D4E5-423E-95BD-04F2A6181AE5}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -235,7 +235,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -331,9 +331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -371,7 +371,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -477,7 +477,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -619,7 +619,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -628,257 +628,257 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D3E7FC6-432C-4BE9-8F62-51CBC091D5C9}">
   <dimension ref="A1:A62"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>49</v>
       </c>
@@ -889,21 +889,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010044526CD282F02A44869A9D2B36E84B2A" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9bdd9e2cf12bb20d6f03de3c45568327">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6a3a5e9b-ee09-41e2-808a-978ed94a5e6b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53d85d7aef2777c68358ab154fcf28f0" ns2:_="">
     <xsd:import namespace="6a3a5e9b-ee09-41e2-808a-978ed94a5e6b"/>
@@ -1047,14 +1032,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CB32E90-60E6-4091-AB6C-EFFB3CC80C0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74FF04ED-1DC9-4E7B-99B9-88A474C113B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6a3a5e9b-ee09-41e2-808a-978ed94a5e6b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1CDAB3-B12F-45FD-94E2-E358F7C41031}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2D1CDAB3-B12F-45FD-94E2-E358F7C41031}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74FF04ED-1DC9-4E7B-99B9-88A474C113B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CB32E90-60E6-4091-AB6C-EFFB3CC80C0D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>